--- a/output/0915__opt/mi455x-gfx1250-kernel-optimization.xlsx
+++ b/output/0915__opt/mi455x-gfx1250-kernel-optimization.xlsx
@@ -17082,7 +17082,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠ 两台机器时钟差约 2 倍，绝对值不可横向比较；本表不做任何时钟换算。</t>
+          <t xml:space="preserve">⚠ 两台机器时钟差约 2 倍，绝对值不可横向比较；本表不做任何时钟换算。所有数值均已回查原始 ledger；与既有文档不一致处以 ledger 为准并在备注说明。</t>
         </is>
       </c>
     </row>
@@ -17349,10 +17349,10 @@
         <v>9.867</v>
       </c>
       <c r="H12">
-        <v>12.412</v>
+        <v>12.454</v>
       </c>
       <c r="I12">
-        <v>620.1</v>
+        <v>618.0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">对起点 +4.28%，51/51 测试绿</t>
+          <t xml:space="preserve">对起点 +4.28%（原始三次 total 12.418/12.455/12.454，取中位）；51/51 测试绿。注：0914 文档记为 12.412 / 620.5，该值在任何 ledger 中均不存在，本表用可溯源的中位数</t>
         </is>
       </c>
     </row>
@@ -17888,7 +17888,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">对基线 4.76×，AC-cycle 后重测</t>
+          <t xml:space="preserve">对基线 4.76×，AC-cycle 后重测。注：文档另记过 11.687(n=7)，穷举该时段 11 条原始记录的全部 7 元子集后确认不可重构（仅 4 个子集命中 fwd1.568+bwd10.118，其 total 均为 11.685），故采用本行</t>
         </is>
       </c>
     </row>

--- a/output/0915__opt/mi455x-gfx1250-kernel-optimization.xlsx
+++ b/output/0915__opt/mi455x-gfx1250-kernel-optimization.xlsx
@@ -17040,136 +17040,334 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:T59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6"/>
-    <col min="2" max="2" width="13"/>
+    <col min="1" max="1" width="4.5"/>
+    <col min="2" max="2" width="12"/>
     <col min="3" max="3" width="15"/>
-    <col min="4" max="4" width="46"/>
-    <col min="5" max="5" width="30"/>
-    <col min="6" max="8" width="10"/>
-    <col min="9" max="9" width="10"/>
-    <col min="10" max="11" width="8"/>
-    <col min="12" max="12" width="26"/>
-    <col min="13" max="13" width="52"/>
+    <col min="4" max="4" width="20"/>
+    <col min="5" max="5" width="31"/>
+    <col min="6" max="6" width="4"/>
+    <col min="7" max="7" width="7"/>
+    <col min="8" max="8" width="5"/>
+    <col min="9" max="9" width="5"/>
+    <col min="10" max="10" width="5"/>
+    <col min="11" max="11" width="7"/>
+    <col min="12" max="14" width="9"/>
+    <col min="15" max="15" width="9"/>
+    <col min="16" max="16" width="13"/>
+    <col min="17" max="17" width="4"/>
+    <col min="18" max="18" width="8"/>
+    <col min="19" max="19" width="22"/>
+    <col min="20" max="20" width="70"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attention — Primus-Turbo on gfx1250</t>
+          <t xml:space="preserve">Attention, Machine: B0-ctheliosp-1b112-a37-1 (4x gfx1250) | A0-heliosr-1b114-c07-1 (1x gfx1250, VR-throttled)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">形状统一 b=4 s=8192 hq=32 hkv=8 d=128 bf16 causal（与 llama-3.1-8B 生产配置逐项一致）。算子级 = 单层一次 fwd+bwd，tune_attention.py：20 iters / 5 warmup / CUDA-event 中位 / 256MiB L2 flush / SQNR 门槛 50dB。</t>
+          <t xml:space="preserve">Maidas Projection</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MX455X Hardware Spec</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TFLOP/s 口径 = 7·b·hq·s²·d / t（含 causal 因子，fwd+bwd），与 0914 已记录值交叉验证一致（偏差 ≤0.07%）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">⚠ 两台机器时钟差约 2 倍，绝对值不可横向比较；本表不做任何时钟换算。所有数值均已回查原始 ledger；与既有文档不一致处以 ledger 为准并在备注说明。</t>
+          <t xml:space="preserve">delivered BF16</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>3470.0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">theoretical BF16</t>
+        </is>
+      </c>
+      <c r="H3">
+        <v>5040.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[1] Operator ladder — one layer, one fwd+bwd, causal. tflop/s = 7*b*hq*s^2*d / t</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">【B0】ctheliosp-1b112-a37-1 — 4× gfx1250，负载下 2133–2244 MHz（健康时钟）</t>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">machine</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sclk(MHz)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fwd impl</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bwd impl</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hq</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hkv</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">d</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dtype</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fwd ms</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bwd ms</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">total ms</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tflop/s</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hardware MFU</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cv</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SQNR out/dq/dk/dv</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">note</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">工作内容：优化 Primus-Turbo 自带的 Triton 融合 attention（0914）</t>
+      <c r="A7">
+        <v>1.0</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B0-a37-1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2133-2244</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton (turbo)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton fused (factory)</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>4.0</v>
+      </c>
+      <c r="G7">
+        <v>8192.0</v>
+      </c>
+      <c r="H7">
+        <v>32.0</v>
+      </c>
+      <c r="I7">
+        <v>8.0</v>
+      </c>
+      <c r="J7">
+        <v>128.0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bf16</t>
+        </is>
+      </c>
+      <c r="L7">
+        <v>2.716</v>
+      </c>
+      <c r="M7">
+        <v>10.292</v>
+      </c>
+      <c r="N7">
+        <v>13.0</v>
+      </c>
+      <c r="O7">
+        <v>592.0</v>
+      </c>
+      <c r="P7">
+        <f>O7/$H$3</f>
+      </c>
+      <c r="Q7">
+        <v>3.0</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.24%</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53.67/52.24/52.31/52.71</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0913 champion — starting point</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#</t>
-        </is>
+      <c r="A8">
+        <v>2.0</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">机器</t>
+          <t xml:space="preserve">B0-a37-1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">sclk(MHz)</t>
+          <t xml:space="preserve">2133-2244</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">实现 / 配置</t>
+          <t xml:space="preserve">Triton (turbo)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">shape</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fwd(ms)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bwd(ms)</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">total(ms)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TFLOP/s</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n</t>
-        </is>
+          <t xml:space="preserve">Triton fused, waves_per_eu unset</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>4.0</v>
+      </c>
+      <c r="G8">
+        <v>8192.0</v>
+      </c>
+      <c r="H8">
+        <v>32.0</v>
+      </c>
+      <c r="I8">
+        <v>8.0</v>
+      </c>
+      <c r="J8">
+        <v>128.0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">离散</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SQNR out/dq/dk/dv</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">备注</t>
+          <t xml:space="preserve">bf16</t>
+        </is>
+      </c>
+      <c r="L8">
+        <v>2.718</v>
+      </c>
+      <c r="M8">
+        <v>9.861</v>
+      </c>
+      <c r="N8">
+        <v>12.58</v>
+      </c>
+      <c r="O8">
+        <v>611.8</v>
+      </c>
+      <c r="P8">
+        <f>O8/$H$3</f>
+      </c>
+      <c r="Q8">
+        <v>3.0</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.06%</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53.67/52.24/52.31/52.71</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gain is in backend-chosen occupancy, not instruction count</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -17183,45 +17381,66 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">起点冠军（Triton 融合）</t>
+          <t xml:space="preserve">Triton, num_warps=2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">b4/s8192/hq32/hkv8/d128 bf16 causal</t>
+          <t xml:space="preserve">Triton fused (factory)</t>
         </is>
       </c>
       <c r="F9">
-        <v>2.716</v>
+        <v>4.0</v>
       </c>
       <c r="G9">
-        <v>10.292</v>
+        <v>8192.0</v>
       </c>
       <c r="H9">
-        <v>13.0</v>
+        <v>32.0</v>
       </c>
       <c r="I9">
-        <v>592.0</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
+        <v>8.0</v>
+      </c>
+      <c r="J9">
+        <v>128.0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.3%</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0913 冠军</t>
+          <t xml:space="preserve">bf16</t>
+        </is>
+      </c>
+      <c r="L9">
+        <v>2.583</v>
+      </c>
+      <c r="M9">
+        <v>10.289</v>
+      </c>
+      <c r="N9">
+        <v>12.875</v>
+      </c>
+      <c r="O9">
+        <v>597.8</v>
+      </c>
+      <c r="P9">
+        <f>O9/$H$3</f>
+      </c>
+      <c r="Q9">
+        <v>3.0</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.38%</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53.67/52.24/52.31/52.71</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -17235,1094 +17454,1269 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">+ waves_per_eu 不设</t>
+          <t xml:space="preserve">Triton, num_warps=2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">b4/s8192/hq32/hkv8/d128 bf16 causal</t>
+          <t xml:space="preserve">Triton fused, waves_per_eu unset</t>
         </is>
       </c>
       <c r="F10">
-        <v>2.718</v>
+        <v>4.0</v>
       </c>
       <c r="G10">
-        <v>9.861</v>
+        <v>8192.0</v>
       </c>
       <c r="H10">
-        <v>12.58</v>
+        <v>32.0</v>
       </c>
       <c r="I10">
-        <v>611.8</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
+        <v>8.0</v>
+      </c>
+      <c r="J10">
+        <v>128.0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.3%</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">收益在后端自选占用率，不在指令数</t>
+          <t xml:space="preserve">bf16</t>
+        </is>
+      </c>
+      <c r="L10">
+        <v>2.579</v>
+      </c>
+      <c r="M10">
+        <v>9.872</v>
+      </c>
+      <c r="N10">
+        <v>12.454</v>
+      </c>
+      <c r="O10">
+        <v>618.0</v>
+      </c>
+      <c r="P10">
+        <f>O10/$H$3</f>
+      </c>
+      <c r="Q10">
+        <v>3.0</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.30%</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53.67/52.24/52.31/52.71</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MERGED new default (566e7798), +4.28% vs row 1. Docs quote 12.412/620.5 — absent from every ledger; median of raw 12.418/12.455/12.454 used here</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11">
+        <v>5.0</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B0-a37-1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2133-2244</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aiter ASM</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton fused</t>
+        </is>
+      </c>
+      <c r="F11">
+        <v>4.0</v>
+      </c>
+      <c r="G11">
+        <v>8192.0</v>
+      </c>
+      <c r="H11">
+        <v>32.0</v>
+      </c>
+      <c r="I11">
+        <v>8.0</v>
+      </c>
+      <c r="J11">
+        <v>128.0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bf16</t>
+        </is>
+      </c>
+      <c r="L11">
+        <v>1.41</v>
+      </c>
+      <c r="M11">
+        <v>9.77</v>
+      </c>
+      <c r="N11">
+        <v>11.147</v>
+      </c>
+      <c r="O11">
+        <v>690.5</v>
+      </c>
+      <c r="P11">
+        <f>O11/$H$3</f>
+      </c>
+      <c r="Q11">
         <v>3.0</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B0-a37-1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2133-2244</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+ fwd num_warps=2</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">b4/s8192/hq32/hkv8/d128 bf16 causal</t>
-        </is>
-      </c>
-      <c r="F11">
-        <v>2.583</v>
-      </c>
-      <c r="G11">
-        <v>10.289</v>
-      </c>
-      <c r="H11">
-        <v>12.875</v>
-      </c>
-      <c r="I11">
-        <v>597.8</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.3%</t>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53.62/52.24/52.31/52.71</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T7 — ASM forward beats the fused reference</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12">
+        <v>6.0</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B0-a37-1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2133-2244</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton (champion)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton fused</t>
+        </is>
+      </c>
+      <c r="F12">
         <v>4.0</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B0-a37-1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2133-2244</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+ 两者合并（新默认）</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">b4/s8192/hq32/hkv8/d128 bf16 causal</t>
-        </is>
-      </c>
-      <c r="F12">
-        <v>2.579</v>
-      </c>
       <c r="G12">
-        <v>9.867</v>
+        <v>8192.0</v>
       </c>
       <c r="H12">
-        <v>12.454</v>
+        <v>32.0</v>
       </c>
       <c r="I12">
-        <v>618.0</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
+        <v>8.0</v>
+      </c>
+      <c r="J12">
+        <v>128.0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.3%</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
+          <t xml:space="preserve">bf16</t>
+        </is>
+      </c>
+      <c r="L12">
+        <v>2.607</v>
+      </c>
+      <c r="M12">
+        <v>9.799</v>
+      </c>
+      <c r="N12">
+        <v>12.406</v>
+      </c>
+      <c r="O12">
+        <v>620.4</v>
+      </c>
+      <c r="P12">
+        <f>O12/$H$3</f>
+      </c>
+      <c r="Q12">
+        <v>3.0</v>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t xml:space="preserve">53.67/52.24/52.31/52.71</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">对起点 +4.28%（原始三次 total 12.418/12.455/12.454，取中位）；51/51 测试绿。注：0914 文档记为 12.412 / 620.5，该值在任何 ledger 中均不存在，本表用可溯源的中位数</t>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">same-window control for the row above</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">B0-a37-1</t>
+          <t xml:space="preserve">A0-c07-1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2133-2244</t>
+          <t xml:space="preserve">1100 (943 meas.)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">aiter ASM 前向 + Triton 融合反向</t>
+          <t xml:space="preserve">Triton (turbo stock)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">b4/s8192/hq32/hkv8/d128 bf16 causal</t>
+          <t xml:space="preserve">Triton fused (stock)</t>
         </is>
       </c>
       <c r="F13">
-        <v>1.41</v>
+        <v>4.0</v>
       </c>
       <c r="G13">
-        <v>9.77</v>
+        <v>8192.0</v>
       </c>
       <c r="H13">
-        <v>11.147</v>
+        <v>32.0</v>
       </c>
       <c r="I13">
-        <v>690.5</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53.62/52.24/52.31/52.71</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">T7：打穿融合参考上界</t>
+        <v>8.0</v>
+      </c>
+      <c r="J13">
+        <v>128.0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bf16</t>
+        </is>
+      </c>
+      <c r="L13">
+        <v>10.651</v>
+      </c>
+      <c r="M13">
+        <v>45.134</v>
+      </c>
+      <c r="N13">
+        <v>55.785</v>
+      </c>
+      <c r="O13">
+        <v>138.0</v>
+      </c>
+      <c r="P13">
+        <f>O13/$H$3</f>
+      </c>
+      <c r="Q13">
+        <v>3.0</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.93%</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53.67/52.24/52.31/52.71</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BASELINE @1cb2e183. Pre-incident; measured from worktree wt-bakeoff</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14">
+        <v>8.0</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A0-c07-1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1100 (943 meas.)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton (forced)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton fused</t>
+        </is>
+      </c>
+      <c r="F14">
+        <v>4.0</v>
+      </c>
+      <c r="G14">
+        <v>8192.0</v>
+      </c>
+      <c r="H14">
+        <v>32.0</v>
+      </c>
+      <c r="I14">
+        <v>8.0</v>
+      </c>
+      <c r="J14">
+        <v>128.0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bf16</t>
+        </is>
+      </c>
+      <c r="L14">
+        <v>4.166</v>
+      </c>
+      <c r="M14">
+        <v>17.835</v>
+      </c>
+      <c r="N14">
+        <v>22.001</v>
+      </c>
+      <c r="O14">
+        <v>349.8</v>
+      </c>
+      <c r="P14">
+        <f>O14/$H$3</f>
+      </c>
+      <c r="Q14">
+        <v>2.0</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.06%</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.54x vs baseline. Pre-incident</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>9.0</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A0-c07-1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1100 (943 meas.)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aiter ASM</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton fused</t>
+        </is>
+      </c>
+      <c r="F15">
+        <v>4.0</v>
+      </c>
+      <c r="G15">
+        <v>8192.0</v>
+      </c>
+      <c r="H15">
+        <v>32.0</v>
+      </c>
+      <c r="I15">
+        <v>8.0</v>
+      </c>
+      <c r="J15">
+        <v>128.0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bf16</t>
+        </is>
+      </c>
+      <c r="L15">
+        <v>1.561</v>
+      </c>
+      <c r="M15">
+        <v>17.686</v>
+      </c>
+      <c r="N15">
+        <v>19.239</v>
+      </c>
+      <c r="O15">
+        <v>400.1</v>
+      </c>
+      <c r="P15">
+        <f>O15/$H$3</f>
+      </c>
+      <c r="Q15">
+        <v>5.0</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.53%</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CURRENT DEFAULT — 2.90x. Post-AC-cycle; pre-incident value was 19.233 (+0.03%), i.e. machine returned to same state</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>10.0</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A0-c07-1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1100 (943 meas.)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aiter ASM</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aiter ASM</t>
+        </is>
+      </c>
+      <c r="F16">
+        <v>4.0</v>
+      </c>
+      <c r="G16">
+        <v>8192.0</v>
+      </c>
+      <c r="H16">
+        <v>32.0</v>
+      </c>
+      <c r="I16">
+        <v>8.0</v>
+      </c>
+      <c r="J16">
+        <v>128.0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bf16</t>
+        </is>
+      </c>
+      <c r="L16">
+        <v>1.572</v>
+      </c>
+      <c r="M16">
+        <v>10.16</v>
+      </c>
+      <c r="N16">
+        <v>11.726</v>
+      </c>
+      <c r="O16">
+        <v>656.4</v>
+      </c>
+      <c r="P16">
+        <f>O16/$H$3</f>
+      </c>
+      <c r="Q16">
+        <v>5.0</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.57%</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">53.62/52.24/50.61/50.83</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.76x. OPT-IN only (PRIMUS_TURBO_ATTN_ENABLE_ASM_BWD=1); default OFF — no measurable e2e gain at n=9. Docs also quote 11.687 (n=7): unreconstructible from any subset of the raw pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>11.0</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A0-c07-1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1100 (943 meas.)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Triton (forced)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aiter ASM</t>
+        </is>
+      </c>
+      <c r="F17">
+        <v>4.0</v>
+      </c>
+      <c r="G17">
+        <v>8192.0</v>
+      </c>
+      <c r="H17">
+        <v>32.0</v>
+      </c>
+      <c r="I17">
+        <v>8.0</v>
+      </c>
+      <c r="J17">
+        <v>128.0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bf16</t>
+        </is>
+      </c>
+      <c r="L17">
+        <v>4.249</v>
+      </c>
+      <c r="M17">
+        <v>10.418</v>
+      </c>
+      <c r="N17">
+        <v>14.666</v>
+      </c>
+      <c r="O17">
+        <v>524.8</v>
+      </c>
+      <c r="P17">
+        <f>O17/$H$3</f>
+      </c>
+      <c r="Q17">
+        <v>3.0</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.84%</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cv far above every other row; cause never investigated</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[2] B0 — knobs measured and REJECTED (bwd only; do not re-walk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">machine</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">knob</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bwd ms</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">note</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>1.0</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B0-a37-1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fused bwd num_warps=2</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>46.984</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">factory 4 is optimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>2.0</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B0-a37-1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fused bwd num_warps=8</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>24.134</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">offline ISA predicted a VGPR win; spill cost dominates — register-pressure hypothesis falsified</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>3.0</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B0-a37-1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fused bwd num_warps=16</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>23.541</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>4.0</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B0-a37-1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fused bwd num_stages=2</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>12.553</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">opposite direction from the forward</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>5.0</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B0-a37-1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BLOCK_M1/N2 = 16</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>12.855</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">factory 32 is optimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
         <v>6.0</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t xml:space="preserve">B0-a37-1</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2133-2244</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">（同窗口对照）Triton 融合冠军</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">b4/s8192/hq32/hkv8/d128 bf16 causal</t>
-        </is>
-      </c>
-      <c r="F14">
-        <v>2.607</v>
-      </c>
-      <c r="G14">
-        <v>9.799</v>
-      </c>
-      <c r="H14">
-        <v>12.406</v>
-      </c>
-      <c r="I14">
-        <v>620.4</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53.67/52.24/52.31/52.71</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">与上一行交替测量</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B0 上已测并否决（别再走一遍）——只记 bwd(ms)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">融合反向 num_warps=2</t>
-        </is>
-      </c>
-      <c r="G17">
-        <v>46.98</v>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">出厂的 4 最优</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">融合反向 num_warps=8</t>
-        </is>
-      </c>
-      <c r="G18">
-        <v>24.13</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">离线 ISA 预测能降 VGPR，实测 spill 代价压倒收益</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">融合反向 num_warps=16</t>
-        </is>
-      </c>
-      <c r="G19">
-        <v>23.54</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">融合反向 num_stages=2</t>
-        </is>
-      </c>
-      <c r="G20">
-        <v>12.55</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">与前向方向相反</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BLOCK_M1/N2 = 16</t>
-        </is>
-      </c>
-      <c r="G21">
-        <v>12.86</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">出厂的 32 最优</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="D22" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t xml:space="preserve">BLOCK_M1/N2 = 64</t>
         </is>
       </c>
-      <c r="G22">
-        <v>23.97</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">waves_per_eu = 2 / 3</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49.68 / 78.75</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">悬崖，不是趋势</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前向 num_warps=8</t>
-        </is>
-      </c>
-      <c r="F24">
-        <v>5.18</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">比出厂的 4 还差，2 是井底</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">【A0】heliosr-1b114-c07-1 — 1× gfx1250，VR 限频。rocm-smi 报 1100MHz，持续负载下 sysfs 实测 943MHz</t>
-        </is>
+      <c r="D26">
+        <v>23.974</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">工作内容：接入 aiter 预编译 ASM 前向/反向，替换出厂实现（0915）</t>
+      <c r="A27">
+        <v>7.0</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B0-a37-1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waves_per_eu = 2</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>49.681</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cliff, not a trend</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#</t>
-        </is>
+      <c r="A28">
+        <v>8.0</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">机器</t>
+          <t xml:space="preserve">B0-a37-1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">sclk(MHz)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">实现 / 配置</t>
-        </is>
+          <t xml:space="preserve">waves_per_eu = 3</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>78.749</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">shape</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fwd(ms)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bwd(ms)</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">total(ms)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TFLOP/s</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">n</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">离散</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SQNR out/dq/dk/dv</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">备注</t>
+          <t xml:space="preserve">cliff, not a trend</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">A0-c07-1</t>
+          <t xml:space="preserve">B0-a37-1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100 (实测943)</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Primus-Turbo 出厂 @1cb2e183（全 Triton）</t>
-        </is>
+          <t xml:space="preserve">fwd num_warps=8</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>5.18</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">b4/s8192/hq32/hkv8/d128 bf16 causal</t>
-        </is>
-      </c>
-      <c r="F29">
-        <v>10.651</v>
-      </c>
-      <c r="G29">
-        <v>45.134</v>
-      </c>
-      <c r="H29">
-        <v>55.785</v>
-      </c>
-      <c r="I29">
-        <v>138.0</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.93%</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">基线</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>2.0</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A0-c07-1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1100 (实测943)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">强制 Triton 前向 + Triton 融合反向</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">b4/s8192/hq32/hkv8/d128 bf16 causal</t>
-        </is>
-      </c>
-      <c r="F30">
-        <v>4.166</v>
-      </c>
-      <c r="G30">
-        <v>17.835</v>
-      </c>
-      <c r="H30">
-        <v>22.001</v>
-      </c>
-      <c r="I30">
-        <v>349.8</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.06%</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">对基线 2.54×</t>
+          <t xml:space="preserve">worse than factory 4; 2 is the floor</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>3.0</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A0-c07-1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1100 (实测943)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aiter ASM 前向 + Triton 融合反向 ← 当前默认</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">b4/s8192/hq32/hkv8/d128 bf16 causal</t>
-        </is>
-      </c>
-      <c r="F31">
-        <v>1.561</v>
-      </c>
-      <c r="G31">
-        <v>17.686</v>
-      </c>
-      <c r="H31">
-        <v>19.239</v>
-      </c>
-      <c r="I31">
-        <v>400.1</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.53%</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">对基线 2.90×，AC-cycle 后重测</t>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[3] A0 — ASM-backward eligibility gate. ratio = fused bwd / ASM bwd, &gt;1 means ASM wins. Backward only, mean of n=2</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>4.0</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">seqlen \ b*hq</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">A0-c07-1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100 (实测943)</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">aiter ASM 前向 + ASM 反向（默认关闭，需显式开启）</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">b4/s8192/hq32/hkv8/d128 bf16 causal</t>
-        </is>
-      </c>
-      <c r="F32">
-        <v>1.572</v>
-      </c>
-      <c r="G32">
-        <v>10.16</v>
-      </c>
-      <c r="H32">
-        <v>11.726</v>
-      </c>
-      <c r="I32">
-        <v>656.4</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.57%</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53.62/52.24/50.61/50.83</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">对基线 4.76×，AC-cycle 后重测。注：文档另记过 11.687(n=7)，穷举该时段 11 条原始记录的全部 7 元子集后确认不可重构（仅 4 个子集命中 fwd1.568+bwd10.118，其 total 均为 11.685），故采用本行</t>
+          <t xml:space="preserve">24</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gate threshold: seqlen &gt;= 2048</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>5.0</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1024</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">A0-c07-1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1100 (实测943)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">强制 Triton 前向 + ASM 反向</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">b4/s8192/hq32/hkv8/d128 bf16 causal</t>
-        </is>
-      </c>
-      <c r="F33">
-        <v>4.249</v>
-      </c>
-      <c r="G33">
-        <v>10.418</v>
-      </c>
-      <c r="H33">
-        <v>14.666</v>
-      </c>
-      <c r="I33">
-        <v>524.8</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10.84%</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仅 RESULTS.md 有，离散大</t>
+          <t xml:space="preserve">0.660</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.632</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.537</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1536</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.869</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">A0：ASM 反向资格门（比值 = 融合反向 ÷ ASM 反向，&gt;1 表示 ASM 更快；每格 n=2 取均值）</t>
+          <t xml:space="preserve">2048</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.748</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.549</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">seqlen \ b·hq</t>
+          <t xml:space="preserve">4096</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2.812</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2.025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2.571</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">2.235</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128</t>
+          <t xml:space="preserve">2.110</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024</t>
+          <t xml:space="preserve">8192</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.660</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.632</t>
+          <t xml:space="preserve">3.954</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.537</t>
+          <t xml:space="preserve">2.002</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1536</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0.869</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2048 ← 门槛</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.748</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.549</t>
+          <t xml:space="preserve">ASM bwd fixed floor (NOT in the columns above — indexed by seqlen, not by b*hq): 0.88 ms @ s1024 / 0.91 @ s2048 / 1.00 @ s4096 / 1.34 @ s8192 — near-constant across 16x work, i.e. ~0.85 ms of fixed per-call cost, which is what the seqlen floor exists to amortise.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4096</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.812</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.025</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.571</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.235</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.110</t>
+          <t xml:space="preserve">[4] A0 — end-to-end, llama-3.1-8B, 8 layers, b=4 s=8192, 1 GPU, AC=none, compile off, seed pinned, n=9 per arm</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8192</t>
+          <t xml:space="preserve">config</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.954</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.002</t>
+          <t xml:space="preserve">tps</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MFU</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">between-run sd</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">modes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">note</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASM 反向固定地板：seqlen 1024/2048/4096/8192 下耗时 0.88/0.91/1.00/1.34 ms —— 跨 16 倍工作量近乎常数，约 0.85ms 固定开销，故需 seqlen≥2048 才摊得开</t>
+          <t xml:space="preserve">baseline</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>6128.0</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~34%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.91%</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5822x2 | 5936x2 | 6327x5</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trimodal — traced to hipBLASLt's NN GridBased lookup table</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠ 这 9 个点测的是【未修复】的调用路径（tune_attention.py:529 / t2_bringup.py:224,266 / perfdq_diag.py:18 均未传 hip= 与 scratch=，只有产品路径传了）。</t>
+          <t xml:space="preserve">+ GEMM layout workaround</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>11604.0</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65.4%</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.42%</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11604x9 (unimodal)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.894x. Zero accuracy cost: SQNR identical to the original path</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  固定地板里有一部分正是每次调用的 hipModuleLoad；修复后重测得 8.13–8.68ms（而非 10.16），即算子级比值实际约 2.18× 而非 1.74×。门槛很可能定高了，需重测。</t>
+          <t xml:space="preserve">ASM bwd ON / OFF (no workaround)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6110.8 / 6128.1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.88% / 3.91%</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-0.28%, 0.15x sem — not significant; hence ASM bwd defaults OFF</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">【A0】端到端（llama-3.1-8B，8 层配置，b=4 s=8192，单卡，AC=none，compile 关，种子已钉，每臂 n=9）</t>
+          <t xml:space="preserve">[5] A0 — where a step goes (8 layers, step-10 torch profile, 5.2 s step)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">配置</t>
+          <t xml:space="preserve">module</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">tps</t>
+          <t xml:space="preserve">ms</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">MFU</t>
+          <t xml:space="preserve">share</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">跨运行 sd</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">模态</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">备注</t>
+          <t xml:space="preserve">note</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">基线</t>
+          <t xml:space="preserve">hipBLASLt GEMM</t>
         </is>
       </c>
       <c r="B48">
-        <v>6128.0</v>
+        <v>4877.0</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">~34%</t>
+          <t xml:space="preserve">94%</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.91%</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5822×2 | 5936×2 | 6327×5</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">三模态，源自 hipBLASLt NN 路径查找表</t>
+          <t xml:space="preserve">4727 ms of it (97%) on MT32x16x32 — the wrong solution</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">+ GEMM 布局修法 (bin/nkfix.py)</t>
+          <t xml:space="preserve">attention (fwd+bwd)</t>
         </is>
       </c>
       <c r="B49">
-        <v>11604.0</v>
+        <v>171.0</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">65.4%</t>
+          <t xml:space="preserve">3.3%</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.42%</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11604×9（单一）</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.894×；精度零代价，SQNR 与原路径逐位相同</t>
+          <t xml:space="preserve">bwd_kernel_causal 138.55 + attn_fwd 32.09</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASM 反向 开 / 关（均无修法）</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6110.8 / 6128.1</t>
+          <t xml:space="preserve">everything else</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>140.0</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.7%</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.88% / 3.91%</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">差异 −0.28%，0.15×sem，统计上不显著 → 故默认关闭</t>
+          <t xml:space="preserve">elementwise / optimizer / reduce / softmax</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">【A0】单步时间构成（8 层，step-10 torch profile，单步 5.2s）</t>
+          <t xml:space="preserve">NOTES</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">模块</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">ms</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">占比</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">备注</t>
+          <t xml:space="preserve">Clocks differ ~2x between the two machines. Absolute values are NOT comparable across machines; no clock conversion is applied anywhere in this sheet.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">hipBLASLt GEMM</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>4877.0</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">94%</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">其中 4727ms（97%）跑在 MT32x16x32 坏 solution 上</t>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A0 is VR-throttled: rocm-smi reports 1100 MHz, a sysfs sample under sustained load read 943 MHz. Its Hardware MFU column is therefore not a measure of efficiency.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">attention（fwd+bwd）</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>171.0</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.3%</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bwd_kernel_causal 138.55 + attn_fwd 32.09</t>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every value re-derived from the raw ledgers. Where a published document disagreed, the ledger wins and the note says so. See LEDGER-AUDIT.md.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">其余全部</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>140.0</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.7%</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">逐元素 / optimizer / 归约 / softmax</t>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rows [3] were measured through the UNFIXED call path — tune_attention.py:529, t2_bringup.py:224/266, perfdq_diag.py:18 pass neither hip= nor scratch=; only the product path does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Part of the 0.85 ms floor IS the per-call hipModuleLoad. Re-measuring the fixed path gives 8.13-8.68 ms (not 10.16), i.e. ~2.18x rather than 1.74x. The gate threshold is likely set too high and needs re-taking.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">※ 交叉验证：B0 满频机器上 torch.mm(NN) 亦仅 112.98 TF/s，对朴素 Triton 的 1190.07 差 10.5× —— 与 A0 的 13× 同源。说明 hipBLASLt 缺 NN 纯 GEMM 调优库不是 A0 限频机器特有，满频机器同样命中。详见 GEMM-NN-FINDING.md</t>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ledger impl_note is unreliable: it is a string assigned from --impl before anything runs. The auditable field is asm_fwd; the SQNR fingerprint (dk 50.61 / dv 50.83 vs the fused path's 52.31 / 52.71) is what proves the ASM backward ran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cross-check: B0 at full clock also measures torch.mm(NN) at just 112.98 tflop/s against 1190.07 for a naive Triton GEMM (10.5x) — same order as A0's 13x. The missing NN tuning library is not specific to the throttled box.</t>
         </is>
       </c>
     </row>

--- a/output/0915__opt/mi455x-gfx1250-kernel-optimization.xlsx
+++ b/output/0915__opt/mi455x-gfx1250-kernel-optimization.xlsx
@@ -18444,7 +18444,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">MFU</t>
+          <t xml:space="preserve">tflop/s (measured)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -18474,7 +18474,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">~34%</t>
+          <t xml:space="preserve">~106</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -18496,7 +18496,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">+ GEMM layout workaround</t>
+          <t xml:space="preserve">+ dgrad layout fix</t>
         </is>
       </c>
       <c r="B43">
@@ -18504,7 +18504,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">65.4%</t>
+          <t xml:space="preserve">~204</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cross-check: B0 at full clock also measures torch.mm(NN) at just 112.98 tflop/s against 1190.07 for a naive Triton GEMM (10.5x) — same order as A0's 13x. The missing NN tuning library is not specific to the throttled box.</t>
+          <t xml:space="preserve">DO NOT quote MFU from any torchtitan log on this box: get_peak_flops() falls back to "assume A100" (312 TF/s) for an unrecognised device_name, and this box reports "AMD Radeon Graphics". The tflop/s column is correct; mfu is not. || Cross-check: B0 at full clock also measures torch.mm(NN) at just 112.98 tflop/s against 1190.07 for a naive Triton GEMM (10.5x) — same order as A0's 13x. The missing NN tuning library is not specific to the throttled box.</t>
         </is>
       </c>
     </row>

--- a/output/0915__opt/mi455x-gfx1250-kernel-optimization.xlsx
+++ b/output/0915__opt/mi455x-gfx1250-kernel-optimization.xlsx
@@ -17040,7 +17040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T59"/>
+  <dimension ref="A1:T60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.5"/>
@@ -18526,195 +18526,225 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t xml:space="preserve">+ wgrad layout fix (0916)</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>38043.0</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">640.7</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.97%</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n=6 (excl. first run: 37738, sd 0.09%)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.21x over unpatched, 3.28x over dgrad-only. Both operands must change: A.contiguous() AND B N-major -- either alone stays on the bad tile (60-70 TF/s). Step 861 ms. Peak memory unchanged at 141.00 GiB. 5 consecutive runs, zero card faults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t xml:space="preserve">ASM bwd ON / OFF (no workaround)</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t xml:space="preserve">6110.8 / 6128.1</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t xml:space="preserve">3.88% / 3.91%</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t xml:space="preserve">-0.28%, 0.15x sem — not significant; hence ASM bwd defaults OFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[5] A0 — where a step goes (8 layers, step-10 torch profile, 5.2 s step)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">module</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ms</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">share</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">note</t>
+          <t xml:space="preserve">[5] A0 — where a step goes (8 layers, step-10 torch profile, 5.2 s step)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">hipBLASLt GEMM</t>
-        </is>
-      </c>
-      <c r="B48">
-        <v>4877.0</v>
+          <t xml:space="preserve">module</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ms</t>
+        </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">94%</t>
+          <t xml:space="preserve">share</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4727 ms of it (97%) on MT32x16x32 — the wrong solution</t>
+          <t xml:space="preserve">note</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">attention (fwd+bwd)</t>
+          <t xml:space="preserve">hipBLASLt GEMM</t>
         </is>
       </c>
       <c r="B49">
-        <v>171.0</v>
+        <v>4877.0</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.3%</t>
+          <t xml:space="preserve">94%</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">bwd_kernel_causal 138.55 + attn_fwd 32.09</t>
+          <t xml:space="preserve">4727 ms of it (97%) on MT32x16x32 — the wrong solution</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t xml:space="preserve">attention (fwd+bwd)</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>171.0</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.3%</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bwd_kernel_causal 138.55 + attn_fwd 32.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t xml:space="preserve">everything else</t>
         </is>
       </c>
-      <c r="B50">
+      <c r="B51">
         <v>140.0</v>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t xml:space="preserve">2.7%</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t xml:space="preserve">elementwise / optimizer / reduce / softmax</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOTES</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clocks differ ~2x between the two machines. Absolute values are NOT comparable across machines; no clock conversion is applied anywhere in this sheet.</t>
+          <t xml:space="preserve">NOTES</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">A0 is VR-throttled: rocm-smi reports 1100 MHz, a sysfs sample under sustained load read 943 MHz. Its Hardware MFU column is therefore not a measure of efficiency.</t>
+          <t xml:space="preserve">Clocks differ ~2x between the two machines. Absolute values are NOT comparable across machines; no clock conversion is applied anywhere in this sheet.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every value re-derived from the raw ledgers. Where a published document disagreed, the ledger wins and the note says so. See LEDGER-AUDIT.md.</t>
+          <t xml:space="preserve">A0 is VR-throttled: rocm-smi reports 1100 MHz, a sysfs sample under sustained load read 943 MHz. Its Hardware MFU column is therefore not a measure of efficiency.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every value re-derived from the raw ledgers. Where a published document disagreed, the ledger wins and the note says so. See LEDGER-AUDIT.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t xml:space="preserve">Rows [3] were measured through the UNFIXED call path — tune_attention.py:529, t2_bringup.py:224/266, perfdq_diag.py:18 pass neither hip= nor scratch=; only the product path does.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" t="inlineStr">
+    <row r="58">
+      <c r="B58" t="inlineStr">
         <is>
           <t xml:space="preserve">Part of the 0.85 ms floor IS the per-call hipModuleLoad. Re-measuring the fixed path gives 8.13-8.68 ms (not 10.16), i.e. ~2.18x rather than 1.74x. The gate threshold is likely set too high and needs re-taking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ledger impl_note is unreliable: it is a string assigned from --impl before anything runs. The auditable field is asm_fwd; the SQNR fingerprint (dk 50.61 / dv 50.83 vs the fused path's 52.31 / 52.71) is what proves the ASM backward ran.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ledger impl_note is unreliable: it is a string assigned from --impl before anything runs. The auditable field is asm_fwd; the SQNR fingerprint (dk 50.61 / dv 50.83 vs the fused path's 52.31 / 52.71) is what proves the ASM backward ran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t xml:space="preserve">DO NOT quote MFU from any torchtitan log on this box: get_peak_flops() falls back to "assume A100" (312 TF/s) for an unrecognised device_name, and this box reports "AMD Radeon Graphics". The tflop/s column is correct; mfu is not. || Cross-check: B0 at full clock also measures torch.mm(NN) at just 112.98 tflop/s against 1190.07 for a naive Triton GEMM (10.5x) — same order as A0's 13x. The missing NN tuning library is not specific to the throttled box.</t>
         </is>

--- a/output/0915__opt/mi455x-gfx1250-kernel-optimization.xlsx
+++ b/output/0915__opt/mi455x-gfx1250-kernel-optimization.xlsx
@@ -17040,7 +17040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T60"/>
+  <dimension ref="A1:T61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.5"/>
@@ -18556,195 +18556,225 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t xml:space="preserve">32-LAYER PRODUCTION config (b=4 s=8192, 20 steps)</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>11608.0</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">steady jitter &lt;0.4%</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n=1 run, 13 steady steps</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.85x vs unpatched 1,984 (6.25x vs 1,858). Step 16.5s -&gt; 2.82s. Peak memory 88.32% vs unpatched 87.98%. THIS is the number to quote -- the 8-layer rows exist to make A/B affordable and are not comparable to a 32-layer result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t xml:space="preserve">ASM bwd ON / OFF (no workaround)</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t xml:space="preserve">6110.8 / 6128.1</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t xml:space="preserve">3.88% / 3.91%</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t xml:space="preserve">-0.28%, 0.15x sem — not significant; hence ASM bwd defaults OFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[5] A0 — where a step goes (8 layers, step-10 torch profile, 5.2 s step)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">module</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ms</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">share</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">note</t>
+          <t xml:space="preserve">[5] A0 — where a step goes (8 layers, step-10 torch profile, 5.2 s step)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">hipBLASLt GEMM</t>
-        </is>
-      </c>
-      <c r="B49">
-        <v>4877.0</v>
+          <t xml:space="preserve">module</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ms</t>
+        </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">94%</t>
+          <t xml:space="preserve">share</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4727 ms of it (97%) on MT32x16x32 — the wrong solution</t>
+          <t xml:space="preserve">note</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">attention (fwd+bwd)</t>
+          <t xml:space="preserve">hipBLASLt GEMM</t>
         </is>
       </c>
       <c r="B50">
-        <v>171.0</v>
+        <v>4877.0</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.3%</t>
+          <t xml:space="preserve">94%</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">bwd_kernel_causal 138.55 + attn_fwd 32.09</t>
+          <t xml:space="preserve">4727 ms of it (97%) on MT32x16x32 — the wrong solution</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t xml:space="preserve">attention (fwd+bwd)</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>171.0</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.3%</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bwd_kernel_causal 138.55 + attn_fwd 32.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t xml:space="preserve">everything else</t>
         </is>
       </c>
-      <c r="B51">
+      <c r="B52">
         <v>140.0</v>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t xml:space="preserve">2.7%</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t xml:space="preserve">elementwise / optimizer / reduce / softmax</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOTES</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clocks differ ~2x between the two machines. Absolute values are NOT comparable across machines; no clock conversion is applied anywhere in this sheet.</t>
+          <t xml:space="preserve">NOTES</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">A0 is VR-throttled: rocm-smi reports 1100 MHz, a sysfs sample under sustained load read 943 MHz. Its Hardware MFU column is therefore not a measure of efficiency.</t>
+          <t xml:space="preserve">Clocks differ ~2x between the two machines. Absolute values are NOT comparable across machines; no clock conversion is applied anywhere in this sheet.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every value re-derived from the raw ledgers. Where a published document disagreed, the ledger wins and the note says so. See LEDGER-AUDIT.md.</t>
+          <t xml:space="preserve">A0 is VR-throttled: rocm-smi reports 1100 MHz, a sysfs sample under sustained load read 943 MHz. Its Hardware MFU column is therefore not a measure of efficiency.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Every value re-derived from the raw ledgers. Where a published document disagreed, the ledger wins and the note says so. See LEDGER-AUDIT.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t xml:space="preserve">Rows [3] were measured through the UNFIXED call path — tune_attention.py:529, t2_bringup.py:224/266, perfdq_diag.py:18 pass neither hip= nor scratch=; only the product path does.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" t="inlineStr">
+    <row r="59">
+      <c r="B59" t="inlineStr">
         <is>
           <t xml:space="preserve">Part of the 0.85 ms floor IS the per-call hipModuleLoad. Re-measuring the fixed path gives 8.13-8.68 ms (not 10.16), i.e. ~2.18x rather than 1.74x. The gate threshold is likely set too high and needs re-taking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ledger impl_note is unreliable: it is a string assigned from --impl before anything runs. The auditable field is asm_fwd; the SQNR fingerprint (dk 50.61 / dv 50.83 vs the fused path's 52.31 / 52.71) is what proves the ASM backward ran.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ledger impl_note is unreliable: it is a string assigned from --impl before anything runs. The auditable field is asm_fwd; the SQNR fingerprint (dk 50.61 / dv 50.83 vs the fused path's 52.31 / 52.71) is what proves the ASM backward ran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t xml:space="preserve">DO NOT quote MFU from any torchtitan log on this box: get_peak_flops() falls back to "assume A100" (312 TF/s) for an unrecognised device_name, and this box reports "AMD Radeon Graphics". The tflop/s column is correct; mfu is not. || Cross-check: B0 at full clock also measures torch.mm(NN) at just 112.98 tflop/s against 1190.07 for a naive Triton GEMM (10.5x) — same order as A0's 13x. The missing NN tuning library is not specific to the throttled box.</t>
         </is>
